--- a/artfynd/A 45969-2023 artfynd.xlsx
+++ b/artfynd/A 45969-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45969-2023 artfynd.xlsx
+++ b/artfynd/A 45969-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97364599</v>
+        <v>97364558</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541700.9011198004</v>
+        <v>541951</v>
       </c>
       <c r="R2" t="n">
-        <v>7016602.572478758</v>
+        <v>7016467</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-10-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97364600</v>
+        <v>97364560</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541702.8438581629</v>
+        <v>541826</v>
       </c>
       <c r="R3" t="n">
-        <v>7016591.793948364</v>
+        <v>7016416</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2021-10-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97364558</v>
+        <v>97364599</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541951.4955425499</v>
+        <v>541701</v>
       </c>
       <c r="R4" t="n">
-        <v>7016466.728710595</v>
+        <v>7016602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2021-10-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97364605</v>
+        <v>97364601</v>
       </c>
       <c r="B5" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541762.8191088527</v>
+        <v>541654</v>
       </c>
       <c r="R5" t="n">
-        <v>7016520.546035481</v>
+        <v>7016610</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,21 +1046,11 @@
           <t>2021-10-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-08</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1119,6 +1059,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1139,37 +1084,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97364601</v>
+        <v>97364600</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541653.4736610571</v>
+        <v>541703</v>
       </c>
       <c r="R6" t="n">
-        <v>7016610.061034265</v>
+        <v>7016592</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,21 +1152,11 @@
           <t>2021-10-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-10-08</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1235,11 +1165,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1260,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97364560</v>
+        <v>97364605</v>
       </c>
       <c r="B7" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541825.9458324204</v>
+        <v>541763</v>
       </c>
       <c r="R7" t="n">
-        <v>7016415.125027497</v>
+        <v>7016521</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,19 +1253,9 @@
           <t>2021-10-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 45969-2023 artfynd.xlsx
+++ b/artfynd/A 45969-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364558</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364560</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364599</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364601</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364600</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,8 +1313,21 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364605</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>